--- a/technical_assessment_by_job/questions/spring boot_questions.xlsx
+++ b/technical_assessment_by_job/questions/spring boot_questions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ws_openai_ws\technical_assessment_by_job\questions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ws_openai\codex_projects\technical_assessment_by_job\questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30159ECD-DECA-4F5D-92A9-4EB8F0C1E2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9587A611-F557-4C48-8B9E-057781D9BDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{FDA89E87-3AF3-4ACE-BFED-809EE8E4600C}"/>
   </bookViews>
@@ -35,10 +35,662 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="213">
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Answer</t>
+  </si>
+  <si>
+    <t>What is Spring Boot?</t>
+  </si>
+  <si>
+    <t>Spring Boot is an extension of the Spring framework that eliminates the boilerplate configurations required for setting up a Spring application. It is opinionated and helps developers create stand-alone, production-grade applications quickly.</t>
+  </si>
+  <si>
+    <t>What are the core features of Spring Boot?</t>
+  </si>
+  <si>
+    <t>The core features include Auto-configuration, Starter dependencies, Spring Boot CLI, and Actuator for production-ready monitoring.</t>
+  </si>
+  <si>
+    <t>What is the @SpringBootApplication annotation?</t>
+  </si>
+  <si>
+    <t>It is a convenience annotation that combines @Configuration, @EnableAutoConfiguration, and @ComponentScan. It is typically placed on the main class of the application.</t>
+  </si>
+  <si>
+    <t>What is Auto-configuration in Spring Boot?</t>
+  </si>
+  <si>
+    <t>Auto-configuration attempts to automatically configure your Spring application based on the jar dependencies that you have added. For example, if 'HSQLDB' is on your classpath, it automatically configures an in-memory database.</t>
+  </si>
+  <si>
+    <t>What are Spring Boot Starters?</t>
+  </si>
+  <si>
+    <t>Starters are a set of convenient dependency descriptors. For instance, 'spring-boot-starter-web' includes all necessary dependencies for web development, including Tomcat and Spring MVC.</t>
+  </si>
+  <si>
+    <t>What is the Spring Boot Actuator?</t>
+  </si>
+  <si>
+    <t>Actuator is a sub-project of Spring Boot that provides production-ready features like health checks, metrics, and auditing via HTTP endpoints or JMX.</t>
+  </si>
+  <si>
+    <t>How does Spring Boot simplify dependency management?</t>
+  </si>
+  <si>
+    <t>By using the 'spring-boot-starter-parent', it manages the versions of all standard dependencies, so developers don't have to manually specify version numbers for every library.</t>
+  </si>
+  <si>
+    <t>What is the difference between Spring and Spring Boot?</t>
+  </si>
+  <si>
+    <t>Spring is a web framework that requires manual configuration (XML or Java-based). Spring Boot is a tool that sits on top of Spring to automate that configuration and provide embedded servers.</t>
+  </si>
+  <si>
+    <t>What are embedded containers in Spring Boot?</t>
+  </si>
+  <si>
+    <t>Spring Boot includes embedded servers like Tomcat, Jetty, or Undertow within the JAR file, so you don't need to install a standalone web server on the host machine.</t>
+  </si>
+  <si>
+    <t>How do you disable specific auto-configuration classes?</t>
+  </si>
+  <si>
+    <t>You can use the 'exclude' attribute of the @SpringBootApplication or @EnableAutoConfiguration annotation.</t>
+  </si>
+  <si>
+    <t>What is the purpose of application.properties or application.yml?</t>
+  </si>
+  <si>
+    <t>These files are used to externalize configuration, allowing you to change settings like server port, database URLs, and logging levels without recompiling code.</t>
+  </si>
+  <si>
+    <t>What are Spring Boot Profiles?</t>
+  </si>
+  <si>
+    <t>Profiles provide a way to segregate parts of your application configuration and make it only available in certain environments (e.g., dev, test, prod).</t>
+  </si>
+  <si>
+    <t>How do you create a Spring Boot project?</t>
+  </si>
+  <si>
+    <t>The most common way is using the Spring Initializr web tool (start.spring.io) or using the Spring Boot CLI.</t>
+  </si>
+  <si>
+    <t>What is the default port for Spring Boot?</t>
+  </si>
+  <si>
+    <t>The default port is 8080.</t>
+  </si>
+  <si>
+    <t>What is the difference between @RestController and @Controller?</t>
+  </si>
+  <si>
+    <t>@RestController is a combination of @Controller and @ResponseBody. It ensures that the return value of methods is written directly to the HTTP response body as JSON or XML.</t>
+  </si>
+  <si>
+    <t>How do you handle exceptions globally in Spring Boot?</t>
+  </si>
+  <si>
+    <t>By using the @ControllerAdvice annotation combined with @ExceptionHandler methods in a global class.</t>
+  </si>
+  <si>
+    <t>What is DevTools in Spring Boot?</t>
+  </si>
+  <si>
+    <t>Spring Boot DevTools is a module that improves development time by providing features like automatic application restarts and LiveReload for the browser.</t>
+  </si>
+  <si>
+    <t>How can you use a custom port in Spring Boot?</t>
+  </si>
+  <si>
+    <t>By setting 'server.port' in application.properties or using a command-line argument like '--server.port=9000'.</t>
+  </si>
+  <si>
+    <t>What is Spring Data JPA?</t>
+  </si>
+  <si>
+    <t>It is a part of the Spring Data project that makes it easy to implement JPA-based repositories. It reduces the amount of boilerplate code required to interact with databases.</t>
+  </si>
+  <si>
+    <t>What is a 'Fat JAR'?</t>
+  </si>
+  <si>
+    <t>A Fat JAR (also known as an executable JAR) contains both the compiled application classes and all its library dependencies in a single file.</t>
+  </si>
+  <si>
+    <t>How do you inject a property value into a Spring Boot bean?</t>
+  </si>
+  <si>
+    <t>Using the @Value annotation, e.g., @Value("${property.name}").</t>
+  </si>
+  <si>
+    <t>What is the use of @ConditionalOnProperty?</t>
+  </si>
+  <si>
+    <t>It allows a bean to be created only if a specific configuration property is present and has a specific value.</t>
+  </si>
+  <si>
+    <t>What is Spring Boot CLI?</t>
+  </si>
+  <si>
+    <t>A command-line tool that can be used to quickly prototype Spring applications using Groovy scripts.</t>
+  </si>
+  <si>
+    <t>How do you enable HTTP/2 in Spring Boot?</t>
+  </si>
+  <si>
+    <t>By setting 'server.http2.enabled=true' in the configuration file, provided the underlying server and SSL/TLS are configured.</t>
+  </si>
+  <si>
+    <t>What is the difference between application.properties and application.yml?</t>
+  </si>
+  <si>
+    <t>Properties uses a flat key-value format. YAML (YML) uses a hierarchical structure which is often easier to read and less repetitive for complex settings.</t>
+  </si>
+  <si>
+    <t>How do you perform integration testing in Spring Boot?</t>
+  </si>
+  <si>
+    <t>By using the @SpringBootTest annotation, which starts the full application context for the test.</t>
+  </si>
+  <si>
+    <t>What is the purpose of @MockBean?</t>
+  </si>
+  <si>
+    <t>It is used in Spring Boot tests to add a mock of a bean into the ApplicationContext, replacing any existing bean of the same type.</t>
+  </si>
+  <si>
+    <t>How can you run code on application startup?</t>
+  </si>
+  <si>
+    <t>By implementing the CommandLineRunner or ApplicationRunner interfaces, which provide a 'run' method that executes after the context is loaded.</t>
+  </si>
+  <si>
+    <t>What is the @ConfigurationProperties annotation?</t>
+  </si>
+  <si>
+    <t>It is used to bind external properties (from application.properties) to a strongly typed Java object.</t>
+  </si>
+  <si>
+    <t>How do you secure a Spring Boot application?</t>
+  </si>
+  <si>
+    <t>By adding the 'spring-boot-starter-security' dependency, which provides default basic authentication and allows for custom security configurations.</t>
+  </si>
+  <si>
+    <t>What is the use of the @Qualifier annotation?</t>
+  </si>
+  <si>
+    <t>It is used to resolve ambiguity when multiple beans of the same type exist in the context, allowing you to specify exactly which one to inject.</t>
+  </si>
+  <si>
+    <t>What is the difference between WAR and JAR packaging in Spring Boot?</t>
+  </si>
+  <si>
+    <t>JAR packaging includes the embedded server and is the preferred 'cloud-native' approach. WAR packaging is used if you want to deploy the application to an external standalone server.</t>
+  </si>
+  <si>
+    <t>How do you reload static content changes without a restart?</t>
+  </si>
+  <si>
+    <t>By using DevTools and ensuring that the IDE is configured to update resources on the classpath.</t>
+  </si>
+  <si>
+    <t>What is the purpose of the @LocalServerPort?</t>
+  </si>
+  <si>
+    <t>It is used in tests to inject the actual HTTP port being used by the server when 'server.port' is set to 0 (random port).</t>
+  </si>
+  <si>
+    <t>What is the use of @JsonIgnore?</t>
+  </si>
+  <si>
+    <t>It is a Jackson annotation used to ignore a specific field or property during JSON serialization/deserialization.</t>
+  </si>
+  <si>
+    <t>How do you connect to an external database like MySQL?</t>
+  </si>
+  <si>
+    <t>Add the MySQL connector dependency and configure 'spring.datasource.url', 'username', and 'password' in application.properties.</t>
+  </si>
+  <si>
+    <t>What is the default logging framework in Spring Boot?</t>
+  </si>
+  <si>
+    <t>Logback is the default logging framework provided by Spring Boot Starters.</t>
+  </si>
+  <si>
+    <t>What is the use of @EnableCaching?</t>
+  </si>
+  <si>
+    <t>It enables Spring's annotation-driven cache management capability.</t>
+  </si>
+  <si>
+    <t>How do you define a custom Error Page?</t>
+  </si>
+  <si>
+    <t>By adding an 'error.html' (or specific status code pages like 404.html) in the /src/main/resources/public/error/ directory.</t>
+  </si>
+  <si>
+    <t>What is Spring Boot's 'Opinionated' approach?</t>
+  </si>
+  <si>
+    <t>It means Spring Boot makes 'reasonable defaults' decisions for you (like which database driver to use or which server to start) to get you running quickly, while still allowing you to override those decisions if needed.</t>
+  </si>
+  <si>
+    <t>Spring Boot is an open-source Java-based framework used to create a micro-service. It is developed by the Pivotal Team and is used to build stand-alone and production-ready spring applications.</t>
+  </si>
+  <si>
+    <t>Mention some advantages of Spring Boot.</t>
+  </si>
+  <si>
+    <t>Advantages include: 1. Easy to understand and develop spring applications. 2. Increases productivity. 3. Reduces development time. 4. No XML configuration required. 5. Embedded servers (Tomcat/Jetty).</t>
+  </si>
+  <si>
+    <t>What are the key features of Spring Boot?</t>
+  </si>
+  <si>
+    <t>Key features: Spring Initializr, Auto-configuration, Starter POMs, Spring Boot Actuator, and CLI.</t>
+  </si>
+  <si>
+    <t>What is Spring Initializr?</t>
+  </si>
+  <si>
+    <t>It is a web tool which allows you to easily create a Spring Boot project structure by providing dependency management and project metadata.</t>
+  </si>
+  <si>
+    <t>It automatically configures your Spring application based on the jar dependencies you have added to the project using the @EnableAutoConfiguration annotation.</t>
+  </si>
+  <si>
+    <t>Starters are a set of convenient dependency descriptors that you can include in your application to get all the Spring and related technology you need without hunting through sample code.</t>
+  </si>
+  <si>
+    <t>What is Spring Boot Actuator?</t>
+  </si>
+  <si>
+    <t>It allows you to monitor and manage your application when you push it to production. It uses HTTP endpoints to check the health, metrics, and state of the app.</t>
+  </si>
+  <si>
+    <t>It is a combination of three annotations: @Configuration, @EnableAutoConfiguration, and @ComponentScan.</t>
+  </si>
+  <si>
+    <t>How can you change the port of a Spring Boot application?</t>
+  </si>
+  <si>
+    <t>By specifying 'server.port=8081' (or any port number) in the application.properties file.</t>
+  </si>
+  <si>
+    <t>What is the Spring Boot DevTools?</t>
+  </si>
+  <si>
+    <t>It is a set of tools that make the development process easier, providing features like automatic restart and LiveReload.</t>
+  </si>
+  <si>
+    <t>What are the types of inner servers supported by Spring Boot?</t>
+  </si>
+  <si>
+    <t>Tomcat (default), Jetty, and Undertow.</t>
+  </si>
+  <si>
+    <t>What is YAML?</t>
+  </si>
+  <si>
+    <t>YAML stands for 'YAML Ain't Markup Language'. It is a human-readable data serialization language used for configuration files in Spring Boot instead of properties files.</t>
+  </si>
+  <si>
+    <t>@RestController is a specialized version of @Controller that includes @ResponseBody, meaning it returns data directly (JSON/XML) rather than a view.</t>
+  </si>
+  <si>
+    <t>It makes it easy to easily implement JPA-based repositories. It helps to improve the implementation of data access layers.</t>
+  </si>
+  <si>
+    <t>How do you define a profile in Spring Boot?</t>
+  </si>
+  <si>
+    <t>Profiles are defined using the @Profile annotation or by creating files like application-dev.properties or application-prod.properties.</t>
+  </si>
+  <si>
+    <t>What is the purpose of @RequestMapping?</t>
+  </si>
+  <si>
+    <t>It is used to map web requests to specific handler classes and/or handler methods.</t>
+  </si>
+  <si>
+    <t>What is the difference between RequestMapping and GetMapping?</t>
+  </si>
+  <si>
+    <t>@GetMapping is a composed annotation that acts as a shortcut for @RequestMapping(method = RequestMethod.GET).</t>
+  </si>
+  <si>
+    <t>What is Dependency Injection?</t>
+  </si>
+  <si>
+    <t>It is a design pattern where the container injects dependent objects into a class, rather than the class creating them itself.</t>
+  </si>
+  <si>
+    <t>Explain the @Autowired annotation.</t>
+  </si>
+  <si>
+    <t>It is used for automatic dependency injection. Spring’s bean factory will resolve and inject the collaborating beans into your bean.</t>
+  </si>
+  <si>
+    <t>What is the default scope of a Bean in Spring?</t>
+  </si>
+  <si>
+    <t>Singleton.</t>
+  </si>
+  <si>
+    <t>It is a command-line tool that allows you to create Spring applications using Groovy scripts.</t>
+  </si>
+  <si>
+    <t>How do you disable a specific auto-configuration?</t>
+  </si>
+  <si>
+    <t>Using @SpringBootApplication(exclude = {DataSourceAutoConfiguration.class}).</t>
+  </si>
+  <si>
+    <t>What is the @PathVariable annotation?</t>
+  </si>
+  <si>
+    <t>It is used to extract values from the URI path of the request.</t>
+  </si>
+  <si>
+    <t>What is the @RequestParam annotation?</t>
+  </si>
+  <si>
+    <t>It is used to extract query parameters from the request URL.</t>
+  </si>
+  <si>
+    <t>What is a Spring Boot Banner?</t>
+  </si>
+  <si>
+    <t>It is the ASCII art printed when the application starts. You can customize it by adding a banner.txt file to your classpath.</t>
+  </si>
+  <si>
+    <t>What is the use of the @Value annotation?</t>
+  </si>
+  <si>
+    <t>It is used to inject values from properties files into bean fields.</t>
+  </si>
+  <si>
+    <t>Properties files use key-value pairs, while YML uses a hierarchical/indented structure. YML is more readable for complex configurations.</t>
+  </si>
+  <si>
+    <t>What is the default embedded server in Spring Boot?</t>
+  </si>
+  <si>
+    <t>Apache Tomcat.</t>
+  </si>
+  <si>
+    <t>Explain Thymeleaf.</t>
+  </si>
+  <si>
+    <t>It is a modern server-side Java template engine for web and standalone environments, often used as the view layer in Spring Boot apps.</t>
+  </si>
+  <si>
+    <t>How to connect Spring Boot to a Database?</t>
+  </si>
+  <si>
+    <t>By adding the database driver dependency and configuring connection details (URL, username, password) in application.properties.</t>
+  </si>
+  <si>
+    <t>What is the purpose of Spring Boot Actuator /health endpoint?</t>
+  </si>
+  <si>
+    <t>It provides basic information about the application's health (e.g., UP or DOWN status).</t>
+  </si>
+  <si>
+    <t>What is a Bean in Spring?</t>
+  </si>
+  <si>
+    <t>A Bean is an object that is instantiated, assembled, and managed by a Spring IoC container.</t>
+  </si>
+  <si>
+    <t>What is the @ComponentScan annotation?</t>
+  </si>
+  <si>
+    <t>It tells Spring which packages to scan for annotated components (Beans, Controllers, Services).</t>
+  </si>
+  <si>
+    <t>What is the @Service annotation?</t>
+  </si>
+  <si>
+    <t>It is used to mark a class that performs business logic.</t>
+  </si>
+  <si>
+    <t>What is the @Repository annotation?</t>
+  </si>
+  <si>
+    <t>It is used to indicate that the class provides the mechanism for storage, retrieval, search, update, and delete operation on objects.</t>
+  </si>
+  <si>
+    <t>What is the @Entity annotation?</t>
+  </si>
+  <si>
+    <t>It specifies that the class is an entity and is mapped to a database table.</t>
+  </si>
+  <si>
+    <t>Spring is a full-featured web framework requiring manual configuration; Spring Boot is an extension that offers auto-configuration for faster development.</t>
+  </si>
+  <si>
+    <t>How to run a Spring Boot JAR file?</t>
+  </si>
+  <si>
+    <t>Using the command: java -jar name_of_jar_file.jar</t>
+  </si>
+  <si>
+    <t>What is Spring AOP?</t>
+  </si>
+  <si>
+    <t>Aspect-Oriented Programming allows you to separate cross-cutting concerns (logging, security) from the main business logic.</t>
+  </si>
+  <si>
+    <t>What is a 'Join Point' in AOP?</t>
+  </si>
+  <si>
+    <t>A point during the execution of a program, such as the execution of a method or the handling of an exception.</t>
+  </si>
+  <si>
+    <t>What is a 'Pointcut' in AOP?</t>
+  </si>
+  <si>
+    <t>A predicate that matches join points.</t>
+  </si>
+  <si>
+    <t>How do you implement security in Spring Boot?</t>
+  </si>
+  <si>
+    <t>By adding the 'spring-boot-starter-security' dependency and creating a configuration class extending WebSecurityConfigurerAdapter.</t>
+  </si>
+  <si>
+    <t>What is H2 Database?</t>
+  </si>
+  <si>
+    <t>It is an open-source, lightweight, in-memory database written in Java. It is often used for testing in Spring Boot.</t>
+  </si>
+  <si>
+    <t>What is the purpose of @Qualifier?</t>
+  </si>
+  <si>
+    <t>It is used alongside @Autowired to resolve ambiguity when there are multiple beans of the same type.</t>
+  </si>
+  <si>
+    <t>What is Spring Boot Batch?</t>
+  </si>
+  <si>
+    <t>It provides reusable functions essential in processing large volumes of records, including logging/tracing, transaction management, and job processing.</t>
+  </si>
+  <si>
+    <t>How to enable Actuator endpoints?</t>
+  </si>
+  <si>
+    <t>By using 'management.endpoints.web.exposure.include=*' in application.properties.</t>
+  </si>
+  <si>
+    <t>What is the @Lazy annotation?</t>
+  </si>
+  <si>
+    <t>It is used to delay the initialization of a bean until it is first requested.</t>
+  </si>
+  <si>
+    <t>What is the @Primary annotation?</t>
+  </si>
+  <si>
+    <t>It indicates that a bean should be given preference when multiple candidates are qualified to autowire a single-valued dependency.</t>
+  </si>
+  <si>
+    <t>What is Spring Boot Logging?</t>
+  </si>
+  <si>
+    <t>Spring Boot uses Commons Logging for all internal logging but leaves the underlying log implementation open. Default configurations for Java Util Logging, Log4J2, and Logback are provided.</t>
+  </si>
+  <si>
+    <t>Explain @Async annotation.</t>
+  </si>
+  <si>
+    <t>It is used to run a method in a separate thread, allowing the main program execution to continue asynchronously.</t>
+  </si>
+  <si>
+    <t>What is MockMvc?</t>
+  </si>
+  <si>
+    <t>It is a class in Spring Test that provides support for Spring MVC testing. It allows you to send HTTP requests and verify responses without starting a full server.</t>
+  </si>
+  <si>
+    <t>What is the purpose of @LocalServerPort?</t>
+  </si>
+  <si>
+    <t>It is used to inject the actual port number used by the embedded server during testing.</t>
+  </si>
+  <si>
+    <t>How do you handle exceptions in Spring Boot?</t>
+  </si>
+  <si>
+    <t>Using @ExceptionHandler at the controller level or @ControllerAdvice for global exception handling.</t>
+  </si>
+  <si>
+    <t>What is the @JsonBackReference annotation?</t>
+  </si>
+  <si>
+    <t>Used in Jackson to handle circular dependencies in JSON serialization (the 'back' part of the relationship).</t>
+  </si>
+  <si>
+    <t>What is the difference between Maven and Gradle?</t>
+  </si>
+  <si>
+    <t>Maven uses XML for project configuration; Gradle uses Groovy or Kotlin DSL. Gradle is generally considered more flexible and faster.</t>
+  </si>
+  <si>
+    <t>What is Spring Cloud?</t>
+  </si>
+  <si>
+    <t>A suite of tools for building common patterns in distributed systems (e.g., configuration management, service discovery, circuit breakers).</t>
+  </si>
+  <si>
+    <t>What is Eureka in Spring Cloud?</t>
+  </si>
+  <si>
+    <t>It is a Service Discovery server that allows microservices to find and communicate with each other without hardcoding IP addresses.</t>
+  </si>
+  <si>
+    <t>What is a Zuul Gateway?</t>
+  </si>
+  <si>
+    <t>An edge service that provides dynamic routing, monitoring, resiliency, and security for microservices.</t>
+  </si>
+  <si>
+    <t>What is Hystrix?</t>
+  </si>
+  <si>
+    <t>A latency and fault tolerance library designed to stop cascading failure and enable resilience in complex distributed systems.</t>
+  </si>
+  <si>
+    <t>How to change the default logging level?</t>
+  </si>
+  <si>
+    <t>By setting 'logging.level.root=WARN' (or other levels) in the properties file.</t>
+  </si>
+  <si>
+    <t>What is the use of @ConditionalOnClass?</t>
+  </si>
+  <si>
+    <t>It matches only when a specified class is present on the classpath.</t>
+  </si>
+  <si>
+    <t>It matches only when a specified property has a specific value.</t>
+  </si>
+  <si>
+    <t>What is Spring Boot Testing?</t>
+  </si>
+  <si>
+    <t>Spring Boot provides @SpringBootTest annotation to search for configuration and start the application context for integration tests.</t>
+  </si>
+  <si>
+    <t>Explain 'Swagger' in Spring Boot.</t>
+  </si>
+  <si>
+    <t>It is a tool used to generate documentation for REST APIs, making it easy for consumers to understand and test endpoints.</t>
+  </si>
+  <si>
+    <t>What is the 'Fat JAR'?</t>
+  </si>
+  <si>
+    <t>A JAR file that contains the classes of the application plus all its dependencies, allowing it to run standalone.</t>
+  </si>
+  <si>
+    <t>How do you reload changes without restarting the server?</t>
+  </si>
+  <si>
+    <t>Using Spring Boot DevTools which includes an 'Embedded LiveReload' server.</t>
+  </si>
+  <si>
+    <t>What is 'Spring Boot Cache'?</t>
+  </si>
+  <si>
+    <t>It provides an abstraction layer to apply caching to methods, significantly improving performance for repeated calls with the same parameters.</t>
+  </si>
+  <si>
+    <t>What is @Cacheable?</t>
+  </si>
+  <si>
+    <t>Indicates that the result of invoking a method (or all methods in a class) can be cached.</t>
+  </si>
+  <si>
+    <t>What is @Scheduled?</t>
+  </si>
+  <si>
+    <t>It is used to execute a method at fixed intervals or at a specific time (Cron expressions).</t>
+  </si>
+  <si>
+    <t>What is the @SpringBootConfiguration annotation?</t>
+  </si>
+  <si>
+    <t>An alternative to @Configuration which indicates that a class provides Spring Boot application configuration.</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -54,7 +706,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -62,12 +714,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,9 +1077,2445 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6678B7BC-ED74-4B70-8D65-A93EA05DBCF3}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C221"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" style="4"/>
+    <col min="2" max="2" width="64.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="4">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="4">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="4">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="4">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="4">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="4">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="4">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="4">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="4">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="4">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="4">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="4">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="4">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="4">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="4">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="4">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="4">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="4">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="4">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="4">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="4">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="4">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="4">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="4">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="4">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="4">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="4">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="4">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="4">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="4">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>28</v>
+      </c>
+      <c r="C55" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" s="4">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="4">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="4">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>34</v>
+      </c>
+      <c r="C58" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="4">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>36</v>
+      </c>
+      <c r="C59" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" s="4">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>38</v>
+      </c>
+      <c r="C60" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" s="4">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>40</v>
+      </c>
+      <c r="C61" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" s="4">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>42</v>
+      </c>
+      <c r="C62" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" s="4">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" s="4">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>46</v>
+      </c>
+      <c r="C64" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" s="4">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>48</v>
+      </c>
+      <c r="C65" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" s="4">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>50</v>
+      </c>
+      <c r="C66" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" s="4">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>52</v>
+      </c>
+      <c r="C67" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" s="4">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>54</v>
+      </c>
+      <c r="C68" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" s="4">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>56</v>
+      </c>
+      <c r="C69" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" s="4">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>58</v>
+      </c>
+      <c r="C70" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" s="4">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>60</v>
+      </c>
+      <c r="C71" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" s="4">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>62</v>
+      </c>
+      <c r="C72" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" s="4">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>64</v>
+      </c>
+      <c r="C73" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" s="4">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>66</v>
+      </c>
+      <c r="C74" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" s="4">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>68</v>
+      </c>
+      <c r="C75" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" s="4">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>70</v>
+      </c>
+      <c r="C76" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" s="4">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>72</v>
+      </c>
+      <c r="C77" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" s="4">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>74</v>
+      </c>
+      <c r="C78" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" s="4">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>76</v>
+      </c>
+      <c r="C79" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" s="4">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>78</v>
+      </c>
+      <c r="C80" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" s="4">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>80</v>
+      </c>
+      <c r="C81" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" s="4">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" s="4">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" s="4">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" s="4">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" s="4">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" s="4">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" s="4">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" s="4">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" s="4">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" s="4">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" s="4">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" s="4">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" s="4">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95" s="4">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96" s="4">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97" s="4">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98" s="4">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" s="4">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" s="4">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" s="4">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102" s="4">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103" s="4">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104" s="4">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" s="4">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106" s="4">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107" s="4">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A108" s="4">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109" s="4">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110" s="4">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111" s="4">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112" s="4">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" s="4">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" s="4">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" s="4">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116" s="4">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117" s="4">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118" s="4">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119" s="4">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A120" s="4">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121" s="4">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A122" s="4">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123" s="4">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A124" s="4">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A125" s="4">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A126" s="4">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127" s="4">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A128" s="4">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129" s="4">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130" s="4">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A131" s="4">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A132" s="4">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A133" s="4">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A134" s="4">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A135" s="4">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A136" s="4">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A137" s="4">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A138" s="4">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A139" s="4">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140" s="4">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A141" s="4">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A142" s="4">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143" s="4">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144" s="4">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145" s="4">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146" s="4">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A147" s="4">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A148" s="4">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A149" s="4">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A150" s="4">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151" s="4">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A152" s="4">
+        <v>151</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153" s="4">
+        <v>152</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A154" s="4">
+        <v>153</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A155" s="4">
+        <v>154</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156" s="4">
+        <v>155</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A157" s="4">
+        <v>156</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158" s="4">
+        <v>157</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A159" s="4">
+        <v>158</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A160" s="4">
+        <v>159</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A161" s="4">
+        <v>160</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A162" s="4">
+        <v>161</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A163" s="4">
+        <v>162</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A164" s="4">
+        <v>163</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A165" s="4">
+        <v>164</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A166" s="4">
+        <v>165</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A167" s="4">
+        <v>166</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168" s="4">
+        <v>167</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A169" s="4">
+        <v>168</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170" s="4">
+        <v>169</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A171" s="4">
+        <v>170</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A172" s="4">
+        <v>171</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A173" s="4">
+        <v>172</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A174" s="4">
+        <v>173</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175" s="4">
+        <v>174</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A176" s="4">
+        <v>175</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A177" s="4">
+        <v>176</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A178" s="4">
+        <v>177</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A179" s="4">
+        <v>178</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A180" s="4">
+        <v>179</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A181" s="4">
+        <v>180</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A182" s="4">
+        <v>181</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A183" s="4">
+        <v>182</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A184" s="4">
+        <v>183</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A185" s="4">
+        <v>184</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A186" s="4">
+        <v>185</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A187" s="4">
+        <v>186</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A188" s="4">
+        <v>187</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A189" s="4">
+        <v>188</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A190" s="4">
+        <v>189</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A191" s="4">
+        <v>190</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A192" s="4">
+        <v>191</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A193" s="4">
+        <v>192</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A194" s="4">
+        <v>193</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A195" s="4">
+        <v>194</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A196" s="4">
+        <v>195</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A197" s="4">
+        <v>196</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A198" s="4">
+        <v>197</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A199" s="4">
+        <v>198</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A200" s="4">
+        <v>199</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A201" s="4">
+        <v>200</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A202" s="4">
+        <v>201</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A203" s="4">
+        <v>202</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A204" s="4">
+        <v>203</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A205" s="4">
+        <v>204</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A206" s="4">
+        <v>205</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A207" s="4">
+        <v>206</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A208" s="4">
+        <v>207</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A209" s="4">
+        <v>208</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A210" s="4">
+        <v>209</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A211" s="4">
+        <v>210</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A212" s="4">
+        <v>211</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A213" s="4">
+        <v>212</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A214" s="4">
+        <v>213</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A215" s="4">
+        <v>214</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A216" s="4">
+        <v>215</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A217" s="4">
+        <v>216</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A218" s="4">
+        <v>217</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A219" s="4">
+        <v>218</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A220" s="4">
+        <v>219</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A221" s="4">
+        <v>220</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>